--- a/artfynd/A 8612-2022 artfynd.xlsx
+++ b/artfynd/A 8612-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8612-2022 artfynd.xlsx
+++ b/artfynd/A 8612-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1329399</v>
+        <v>1155668</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375816.9213147728</v>
+        <v>375817</v>
       </c>
       <c r="R2" t="n">
-        <v>6602664.402383588</v>
+        <v>6602664</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +752,9 @@
           <t>2012-08-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1155668</v>
+        <v>1329399</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375816.9213147728</v>
+        <v>375817</v>
       </c>
       <c r="R3" t="n">
-        <v>6602664.402383588</v>
+        <v>6602664</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -883,19 +863,9 @@
           <t>2012-08-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,132 +894,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1676463</v>
-      </c>
-      <c r="B4" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Skjutsbols by, 150 m N om, Vrm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>375816.9213147728</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6602664.402383588</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Stavnäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2012-08-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Per Larsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Per Larsson, Elvi Eriksson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
